--- a/data/trans_orig/P36BPD03_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD03_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones de verdura u hortalizas que consume al día en 2023</t>
+          <t>Población según el número de raciones de verdura u hortalizas que consume al día en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12084</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37227</t>
+          <t>37670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32025</t>
+          <t>30618</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>20935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51692</t>
+          <t>55392</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121952</t>
+          <t>123411</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>165118</t>
+          <t>166486</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101108</t>
+          <t>99784</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127521</t>
+          <t>127675</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>232472</t>
+          <t>232230</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>288933</t>
+          <t>283084</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,1%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107891</t>
+          <t>105266</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148380</t>
+          <t>148829</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>123654</t>
+          <t>122027</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>151369</t>
+          <t>151387</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>237057</t>
+          <t>237563</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>289883</t>
+          <t>287101</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29983</t>
+          <t>30534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18498</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32671</t>
+          <t>33169</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35929</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58042</t>
+          <t>57289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24704</t>
+          <t>25180</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53681</t>
+          <t>56897</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46620</t>
+          <t>46653</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>56892</t>
+          <t>56195</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>92570</t>
+          <t>94872</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>166855</t>
+          <t>165874</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>223559</t>
+          <t>224825</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125301</t>
+          <t>123824</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162435</t>
+          <t>160946</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>301770</t>
+          <t>303368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>374198</t>
+          <t>374192</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>199463</t>
+          <t>200627</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>258940</t>
+          <t>257912</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251723</t>
+          <t>251359</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>292376</t>
+          <t>293230</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>464195</t>
+          <t>465742</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>540649</t>
+          <t>538060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,07%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41667</t>
+          <t>42844</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81350</t>
+          <t>82778</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53531</t>
+          <t>53454</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81859</t>
+          <t>81784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103679</t>
+          <t>102297</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149618</t>
+          <t>150504</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41186</t>
+          <t>39017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28165</t>
+          <t>27216</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35053</t>
+          <t>35661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61177</t>
+          <t>60730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>90158</t>
+          <t>89836</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>124189</t>
+          <t>125424</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57334</t>
+          <t>57160</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83329</t>
+          <t>83846</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>155470</t>
+          <t>155915</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>198982</t>
+          <t>197788</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98797</t>
+          <t>98115</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131228</t>
+          <t>130885</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148040</t>
+          <t>148297</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179282</t>
+          <t>179086</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>251672</t>
+          <t>255861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>299592</t>
+          <t>301208</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55100</t>
+          <t>55162</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83261</t>
+          <t>84554</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81299</t>
+          <t>81252</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109195</t>
+          <t>109285</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143331</t>
+          <t>143458</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>182875</t>
+          <t>182894</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13957</t>
+          <t>13486</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>15089</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22472</t>
+          <t>22974</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28400</t>
+          <t>28335</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61138</t>
+          <t>57647</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25492</t>
+          <t>24576</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59870</t>
+          <t>59293</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60519</t>
+          <t>58335</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108783</t>
+          <t>107340</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>106102</t>
+          <t>104626</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>147900</t>
+          <t>147024</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>249866</t>
+          <t>248406</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>366916</t>
+          <t>371256</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>365239</t>
+          <t>366179</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>523248</t>
+          <t>521423</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,21%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116324</t>
+          <t>116229</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163092</t>
+          <t>162709</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77891</t>
+          <t>76451</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>165166</t>
+          <t>166666</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>193276</t>
+          <t>199378</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>315636</t>
+          <t>315639</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>416</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>14390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13192</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23048</t>
+          <t>23235</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>106874</t>
+          <t>105925</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>128535</t>
+          <t>127410</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>121758</t>
+          <t>121449</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>141121</t>
+          <t>141803</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>234206</t>
+          <t>233749</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>263254</t>
+          <t>263974</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>42075</t>
+          <t>42733</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>63860</t>
+          <t>63104</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>58431</t>
+          <t>57782</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>77659</t>
+          <t>77377</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>107007</t>
+          <t>106038</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>135654</t>
+          <t>133531</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,53%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22844</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>95348</t>
+          <t>93506</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>125732</t>
+          <t>125181</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>78625</t>
+          <t>78812</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>103912</t>
+          <t>105432</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>183103</t>
+          <t>183431</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>221713</t>
+          <t>219561</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>122890</t>
+          <t>123603</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>152848</t>
+          <t>152640</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>130626</t>
+          <t>130697</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>156078</t>
+          <t>157839</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>259937</t>
+          <t>265008</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>302080</t>
+          <t>301632</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20100</t>
+          <t>22029</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>23189</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20207</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>38904</t>
+          <t>37477</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>58238</t>
+          <t>59314</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>101627</t>
+          <t>99822</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>22235</t>
+          <t>24156</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>78571</t>
+          <t>80167</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>85324</t>
+          <t>78351</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>165380</t>
+          <t>165296</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>81723</t>
+          <t>80601</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>126081</t>
+          <t>125692</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>54403</t>
+          <t>50479</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>156103</t>
+          <t>154389</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>129528</t>
+          <t>127530</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>258301</t>
+          <t>257024</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>168498</t>
+          <t>167008</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>226459</t>
+          <t>225130</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>112935</t>
+          <t>105959</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>291278</t>
+          <t>291387</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>236996</t>
+          <t>262405</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>486292</t>
+          <t>488066</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>221895</t>
+          <t>223249</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>280120</t>
+          <t>280543</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>339992</t>
+          <t>337441</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>647639</t>
+          <t>657741</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>586190</t>
+          <t>584137</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1019521</t>
+          <t>1025059</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,66%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>28895</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>17071</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>45656</t>
+          <t>44715</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>32905</t>
+          <t>37226</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>120592</t>
+          <t>124291</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>71926</t>
+          <t>71486</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>104582</t>
+          <t>107726</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>98976</t>
+          <t>104100</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>208005</t>
+          <t>211343</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>655946</t>
+          <t>656721</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>845567</t>
+          <t>839005</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>494742</t>
+          <t>495957</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>536192</t>
+          <t>536574</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1171381</t>
+          <t>1171494</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1407197</t>
+          <t>1410213</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>44488</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>133620</t>
+          <t>134168</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>85265</t>
+          <t>84503</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>115582</t>
+          <t>115255</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>112998</t>
+          <t>115585</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>236964</t>
+          <t>235684</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>146993</t>
+          <t>147908</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>232120</t>
+          <t>231074</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>122314</t>
+          <t>119156</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>178828</t>
+          <t>176357</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>292912</t>
+          <t>289812</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>391298</t>
+          <t>396371</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>615160</t>
+          <t>611618</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>873605</t>
+          <t>873185</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>552938</t>
+          <t>539289</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>729524</t>
+          <t>727584</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1270836</t>
+          <t>1259283</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1572321</t>
+          <t>1560238</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1634802</t>
+          <t>1630212</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2159107</t>
+          <t>2174827</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1568687</t>
+          <t>1516610</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2025855</t>
+          <t>2013123</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3370696</t>
+          <t>3338519</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3982010</t>
+          <t>4033644</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>546491</t>
+          <t>515693</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>771246</t>
+          <t>769711</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>786749</t>
+          <t>792028</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1443537</t>
+          <t>1492821</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1445624</t>
+          <t>1451596</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2160847</t>
+          <t>2320061</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>32,61%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD03_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD03_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20055</t>
+          <t>18863</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37670</t>
+          <t>30473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>11132</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30618</t>
+          <t>21583</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>32950</t>
+          <t>29995</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20935</t>
+          <t>19715</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55392</t>
+          <t>44427</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>143608</t>
+          <t>131765</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>123411</t>
+          <t>113243</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166486</t>
+          <t>150154</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>114286</t>
+          <t>117984</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>99784</t>
+          <t>104064</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127675</t>
+          <t>131487</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>257894</t>
+          <t>249750</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>232230</t>
+          <t>227079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>283084</t>
+          <t>274720</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>43,27%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>127213</t>
+          <t>137610</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105266</t>
+          <t>119681</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148829</t>
+          <t>156824</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>137099</t>
+          <t>158854</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>122027</t>
+          <t>143239</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>151387</t>
+          <t>173095</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>264312</t>
+          <t>296464</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>237563</t>
+          <t>273418</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>287101</t>
+          <t>319559</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>50,33%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>30606</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>21778</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30534</t>
+          <t>43315</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>28091</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19084</t>
+          <t>21498</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33169</t>
+          <t>36390</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>45920</t>
+          <t>58697</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36700</t>
+          <t>48292</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57289</t>
+          <t>73678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37147</t>
+          <t>36411</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>23083</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56897</t>
+          <t>52007</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>35293</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25985</t>
+          <t>26878</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46653</t>
+          <t>47607</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>72150</t>
+          <t>71703</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>56195</t>
+          <t>56379</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>94872</t>
+          <t>91481</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>194740</t>
+          <t>197438</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>165874</t>
+          <t>170625</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>224825</t>
+          <t>225160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>141686</t>
+          <t>147680</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123824</t>
+          <t>130756</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160946</t>
+          <t>167568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>336426</t>
+          <t>345117</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>303368</t>
+          <t>311302</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>374192</t>
+          <t>379678</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>228151</t>
+          <t>237536</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>200627</t>
+          <t>208439</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257912</t>
+          <t>266528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>272326</t>
+          <t>292501</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251359</t>
+          <t>272794</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>293230</t>
+          <t>314311</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>500478</t>
+          <t>530037</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>465742</t>
+          <t>495566</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>538060</t>
+          <t>568108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,74%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58352</t>
+          <t>59262</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42844</t>
+          <t>43351</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82778</t>
+          <t>79700</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65954</t>
+          <t>71021</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53454</t>
+          <t>56892</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81784</t>
+          <t>86103</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>124306</t>
+          <t>130283</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>102297</t>
+          <t>107631</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>150504</t>
+          <t>152484</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27464</t>
+          <t>25708</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39017</t>
+          <t>37087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27216</t>
+          <t>27447</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>46514</t>
+          <t>44374</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35661</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60730</t>
+          <t>57938</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>106625</t>
+          <t>107962</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>89836</t>
+          <t>91571</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>125424</t>
+          <t>124427</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>69261</t>
+          <t>71299</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57160</t>
+          <t>58632</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83846</t>
+          <t>86290</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>175886</t>
+          <t>179261</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>155915</t>
+          <t>157270</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>197788</t>
+          <t>201312</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>114275</t>
+          <t>116034</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98115</t>
+          <t>100254</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>130885</t>
+          <t>131927</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>163364</t>
+          <t>166000</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148297</t>
+          <t>150093</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179086</t>
+          <t>182321</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>277638</t>
+          <t>282035</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255861</t>
+          <t>259706</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>301208</t>
+          <t>304935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>67686</t>
+          <t>66288</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55162</t>
+          <t>52661</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84554</t>
+          <t>79760</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>95420</t>
+          <t>98357</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81252</t>
+          <t>84389</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>109285</t>
+          <t>113110</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>163107</t>
+          <t>164645</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143458</t>
+          <t>144833</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>182894</t>
+          <t>185412</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>347095</t>
+          <t>354322</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>347095</t>
+          <t>354322</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>347095</t>
+          <t>354322</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>663145</t>
+          <t>670315</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>663145</t>
+          <t>670315</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>663145</t>
+          <t>670315</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13486</t>
+          <t>12739</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15089</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>13193</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22974</t>
+          <t>25656</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>41112</t>
+          <t>42538</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28335</t>
+          <t>29054</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57647</t>
+          <t>61823</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>42413</t>
+          <t>50286</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24576</t>
+          <t>39240</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59293</t>
+          <t>65604</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>83525</t>
+          <t>92824</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58335</t>
+          <t>74746</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107340</t>
+          <t>116362</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>127003</t>
+          <t>149254</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104626</t>
+          <t>124777</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>147024</t>
+          <t>173612</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>296204</t>
+          <t>213931</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>248406</t>
+          <t>195754</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>371256</t>
+          <t>232934</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>423206</t>
+          <t>363185</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>366179</t>
+          <t>332681</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>521423</t>
+          <t>397468</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>50,04%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>138007</t>
+          <t>174888</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116229</t>
+          <t>149368</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>162709</t>
+          <t>200712</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>129602</t>
+          <t>149254</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76451</t>
+          <t>131006</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>166666</t>
+          <t>168190</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>267609</t>
+          <t>324143</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>199378</t>
+          <t>292257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>315639</t>
+          <t>357208</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>311815</t>
+          <t>372377</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>311815</t>
+          <t>372377</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>311815</t>
+          <t>372377</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>787533</t>
+          <t>794338</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>787533</t>
+          <t>794338</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>787533</t>
+          <t>794338</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>435</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>512</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>15196</t>
+          <t>16576</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>10955</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23235</t>
+          <t>24463</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>118037</t>
+          <t>136803</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>105925</t>
+          <t>123974</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>127410</t>
+          <t>147646</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>131755</t>
+          <t>144902</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>121449</t>
+          <t>133903</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>141803</t>
+          <t>155774</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>249791</t>
+          <t>281705</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>233749</t>
+          <t>262998</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>263974</t>
+          <t>297924</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>52082</t>
+          <t>58339</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>42733</t>
+          <t>47556</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>63104</t>
+          <t>70500</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>67578</t>
+          <t>73384</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>57782</t>
+          <t>63169</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>77377</t>
+          <t>83866</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>119659</t>
+          <t>131724</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>106038</t>
+          <t>115782</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>133531</t>
+          <t>148650</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>207968</t>
+          <t>226492</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>207968</t>
+          <t>226492</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>207968</t>
+          <t>226492</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>386710</t>
+          <t>432157</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>386710</t>
+          <t>432157</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>386710</t>
+          <t>432157</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16009</t>
+          <t>16169</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,22 +3605,22 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12273</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>14067</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>21720</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>109970</t>
+          <t>110974</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>93506</t>
+          <t>97644</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>125181</t>
+          <t>124977</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>91565</t>
+          <t>93987</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>78812</t>
+          <t>81985</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>105432</t>
+          <t>107085</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>201535</t>
+          <t>204961</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>183431</t>
+          <t>185713</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>219561</t>
+          <t>224438</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>138287</t>
+          <t>137959</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>123603</t>
+          <t>124911</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>152640</t>
+          <t>152355</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>144572</t>
+          <t>149052</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>130697</t>
+          <t>136901</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>157839</t>
+          <t>162317</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,17 +3866,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>282859</t>
+          <t>287011</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>265008</t>
+          <t>268536</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>301632</t>
+          <t>308109</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,65%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22029</t>
+          <t>20206</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>22701</t>
+          <t>22575</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>28222</t>
+          <t>28418</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>19605</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>37477</t>
+          <t>37932</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>76719</t>
+          <t>84742</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>59314</t>
+          <t>64960</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>99822</t>
+          <t>107167</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>53863</t>
+          <t>62124</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>24156</t>
+          <t>48281</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>80167</t>
+          <t>79558</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>130582</t>
+          <t>146866</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>78351</t>
+          <t>124019</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>165296</t>
+          <t>178628</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>100662</t>
+          <t>118355</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>80601</t>
+          <t>96706</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>125692</t>
+          <t>142644</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>112220</t>
+          <t>130926</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>50479</t>
+          <t>111556</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>154389</t>
+          <t>152325</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>212881</t>
+          <t>249281</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>127530</t>
+          <t>220233</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>257024</t>
+          <t>279908</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>193196</t>
+          <t>223698</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>167008</t>
+          <t>195807</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>225130</t>
+          <t>253321</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>214684</t>
+          <t>258990</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>105959</t>
+          <t>234467</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>291387</t>
+          <t>283775</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>407880</t>
+          <t>482688</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>262405</t>
+          <t>445088</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>488066</t>
+          <t>518621</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>251701</t>
+          <t>289688</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>223249</t>
+          <t>262398</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>280543</t>
+          <t>323740</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>468498</t>
+          <t>320017</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>337441</t>
+          <t>294327</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>657741</t>
+          <t>346689</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>720200</t>
+          <t>609705</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>584137</t>
+          <t>569995</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1025059</t>
+          <t>650192</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>622278</t>
+          <t>716483</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>622278</t>
+          <t>716483</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>622278</t>
+          <t>716483</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1471543</t>
+          <t>1488540</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1471543</t>
+          <t>1488540</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1471543</t>
+          <t>1488540</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>16363</t>
+          <t>18236</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>30632</t>
+          <t>32047</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>25602</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>30602</t>
+          <t>34250</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>23461</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>44715</t>
+          <t>49636</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>83302</t>
+          <t>97069</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>37226</t>
+          <t>79593</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>124291</t>
+          <t>116118</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>85933</t>
+          <t>96411</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>71486</t>
+          <t>80464</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>107726</t>
+          <t>114052</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>169236</t>
+          <t>193481</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>104100</t>
+          <t>168733</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>211343</t>
+          <t>220715</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>735716</t>
+          <t>575063</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>656721</t>
+          <t>550571</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>839005</t>
+          <t>600617</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>516487</t>
+          <t>598591</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>495957</t>
+          <t>575604</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>536574</t>
+          <t>623807</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1252202</t>
+          <t>1173654</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1171494</t>
+          <t>1135174</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1410213</t>
+          <t>1209721</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>74,36%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>92631</t>
+          <t>106982</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>44488</t>
+          <t>87912</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>134168</t>
+          <t>130679</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>99512</t>
+          <t>118581</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>84503</t>
+          <t>99880</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>115255</t>
+          <t>135846</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>192144</t>
+          <t>225564</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>115585</t>
+          <t>197108</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>235684</t>
+          <t>251947</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928012</t>
+          <t>797351</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928012</t>
+          <t>797351</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928012</t>
+          <t>797351</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>716172</t>
+          <t>829598</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>716172</t>
+          <t>829598</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>716172</t>
+          <t>829598</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1644184</t>
+          <t>1626949</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1644184</t>
+          <t>1626949</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1644184</t>
+          <t>1626949</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>192468</t>
+          <t>198818</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>147908</t>
+          <t>166558</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>231074</t>
+          <t>229718</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>149662</t>
+          <t>158776</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>119156</t>
+          <t>135677</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>176357</t>
+          <t>183486</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>342130</t>
+          <t>357595</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>289812</t>
+          <t>321645</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>396371</t>
+          <t>401872</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>788127</t>
+          <t>816110</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>611618</t>
+          <t>762333</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>873185</t>
+          <t>876476</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>664452</t>
+          <t>715142</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>539289</t>
+          <t>673310</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>727584</t>
+          <t>761989</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1452580</t>
+          <t>1531252</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1259283</t>
+          <t>1463105</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1560238</t>
+          <t>1604072</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1781878</t>
+          <t>1713959</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1630212</t>
+          <t>1649591</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2174827</t>
+          <t>1774853</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1876489</t>
+          <t>1982819</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1516610</t>
+          <t>1928696</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2013123</t>
+          <t>2036507</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>3658368</t>
+          <t>3696778</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3338519</t>
+          <t>3609249</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4033644</t>
+          <t>3787107</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>693893</t>
+          <t>799182</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>515693</t>
+          <t>743701</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>769711</t>
+          <t>859366</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>967272</t>
+          <t>873997</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>792028</t>
+          <t>826194</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1492821</t>
+          <t>915618</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>1661166</t>
+          <t>1673179</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1451596</t>
+          <t>1600795</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2320061</t>
+          <t>1746180</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3456366</t>
+          <t>3528069</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3657876</t>
+          <t>3730735</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7114243</t>
+          <t>7258804</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
